--- a/SuppXLS/Scen_SYS_UPD_FF2price.xlsx
+++ b/SuppXLS/Scen_SYS_UPD_FF2price.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\esma\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F87FDBEF-FABF-4698-9580-5EEC6465C730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F70D1BEA-6A1A-497B-9B2D-BD893265F911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25200" yWindow="-21720" windowWidth="77040" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="24" r:id="rId1"/>
